--- a/Opus_Pulse_TNM_vs_Outcome_Model.xlsx
+++ b/Opus_Pulse_TNM_vs_Outcome_Model.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Welcome" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rate Card" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Billing (TNM)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcome" sheetId="4" state="visible" r:id="rId4"/>
@@ -21,12 +21,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,50 +35,89 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00DDEBF7"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="0014315A"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="00222B38"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="006B7480"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="006E7781"/>
+      <color rgb="006B7480"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00222B38"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="006B7480"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
+      <color rgb="002E7D32"/>
+      <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <color rgb="0014315A"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00222B38"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="0014315A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -87,17 +126,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="0014315A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="002F6FB0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F9FD"/>
+        <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4C2"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,31 +151,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00EAF2FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E7F1E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
+        <fgColor rgb="002E7D32"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -141,245 +175,274 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFD3E6"/>
+        <color rgb="00D6DEE8"/>
       </left>
       <right style="thin">
-        <color rgb="00BFD3E6"/>
+        <color rgb="00D6DEE8"/>
       </right>
       <top style="thin">
-        <color rgb="00BFD3E6"/>
+        <color rgb="00D6DEE8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFD3E6"/>
+        <color rgb="00D6DEE8"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFD3E6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFD3E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFD3E6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFD3E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFD3E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFD3E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFD3E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFD3E6"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="009C2B2B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FAE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="002E7D32"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E7F1E8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C2B2B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FAE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C8860D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBF1DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="16"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="002E7D32"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="16"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8860D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -465,7 +528,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Monthly Revenue / Expenses / Profit</a:t>
+              <a:t>Monthly: Revenue / Expenses / Profit</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -485,7 +548,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="2F6FB0"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -503,10 +566,10 @@
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="$#,##0"/>
+          <numFmt formatCode="&quot;$&quot;#,##0"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -527,7 +590,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -569,14 +631,69 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2F6FB0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="14315A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C8860D"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="0AA2C0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="6B7480"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Billing (TNM)'!$A$24:$A$28</f>
+              <f>'Billing (TNM)'!$A$25:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Billing (TNM)'!$D$24:$D$28</f>
+              <f>'Billing (TNM)'!$D$25:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +725,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Client pays  -  TNM vs Outcome</a:t>
+              <a:t>Client pays: TNM vs Outcome</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -623,12 +740,12 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Outcome'!O16</f>
+              <f>'Outcome'!O5</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="6B7480"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -636,12 +753,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$17:$N$18</f>
+              <f>'Outcome'!$N$6:$N$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$O$17:$O$18</f>
+              <f>'Outcome'!$O$6:$O$7</f>
             </numRef>
           </val>
         </ser>
@@ -650,12 +767,12 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Outcome'!P16</f>
+              <f>'Outcome'!P5</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="2E7D32"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -663,20 +780,20 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$17:$N$18</f>
+              <f>'Outcome'!$N$6:$N$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$P$17:$P$18</f>
+              <f>'Outcome'!$P$6:$P$7</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="$#,##0"/>
+          <numFmt formatCode="&quot;$&quot;#,##0"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -697,14 +814,13 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -725,7 +841,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Opus margin %  -  TNM vs Outcome</a:t>
+              <a:t>Opus margin %: TNM vs Outcome</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -740,12 +856,12 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Outcome'!O20</f>
+              <f>'Outcome'!O9</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="6B7480"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -753,12 +869,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$21:$N$22</f>
+              <f>'Outcome'!$N$10:$N$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$O$21:$O$22</f>
+              <f>'Outcome'!$O$10:$O$11</f>
             </numRef>
           </val>
         </ser>
@@ -767,12 +883,12 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Outcome'!P20</f>
+              <f>'Outcome'!P9</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="375623"/>
+              <a:srgbClr val="2E7D32"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -780,20 +896,20 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$21:$N$22</f>
+              <f>'Outcome'!$N$10:$N$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$P$21:$P$22</f>
+              <f>'Outcome'!$P$10:$P$11</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="0%"/>
+          <numFmt formatCode="0.0%"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -814,14 +930,13 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -857,12 +972,12 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Outcome'!O24</f>
+              <f>'Outcome'!O13</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="6B7480"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -870,12 +985,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$25:$N$26</f>
+              <f>'Outcome'!$N$14:$N$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$O$25:$O$26</f>
+              <f>'Outcome'!$O$14:$O$15</f>
             </numRef>
           </val>
         </ser>
@@ -884,12 +999,12 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Outcome'!P24</f>
+              <f>'Outcome'!P13</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7030A0"/>
+              <a:srgbClr val="2F6FB0"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -897,20 +1012,20 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Outcome'!$N$25:$N$26</f>
+              <f>'Outcome'!$N$14:$N$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Outcome'!$P$25:$P$26</f>
+              <f>'Outcome'!$P$14:$P$15</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="$#,##0"/>
+          <numFmt formatCode="&quot;$&quot;#,##0"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -931,14 +1046,13 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -974,12 +1088,34 @@
           <order val="0"/>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="2F6FB0"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2F6FB0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2E7D32"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Dashboard'!$D$5:$D$6</f>
@@ -992,10 +1128,10 @@
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="$#,##0"/>
+          <numFmt formatCode="&quot;$&quot;#,##0"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1016,7 +1152,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1037,7 +1172,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2592000"/>
+    <ext cx="3960000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1083,10 +1218,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2592000"/>
+    <ext cx="3780000" cy="2376000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1105,10 +1240,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2592000"/>
+    <ext cx="3780000" cy="2376000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1127,10 +1262,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2592000"/>
+    <ext cx="3780000" cy="2376000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1157,7 +1292,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2880000"/>
+    <ext cx="4140000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1461,340 +1596,240 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="0014315A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Opus Pulse  -  TNM to Outcome Conversion Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A live model. Change any YELLOW input cell and every result, table and chart recalculates.</t>
-        </is>
-      </c>
+          <t>Opus Pulse - TNM to Outcome Conversion Simulator</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A live model. Change any YELLOW input and every result, table and chart recalculates instantly.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tabs in this workbook</t>
-        </is>
-      </c>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>are the only inputs you edit - team, rates, calendar, expenses, capacity, efficiency and discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Everything else</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>is a live, IFERROR-guarded formula - no #DIV/0! or #N/A, even mid-edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>read from the formula cells, so they redraw automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>The tabs</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Rate Card</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Master billing rate per role x experience. The Billing tab looks rates up from here (INDEX/MATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Standard billing rate per role and experience. Billing looks rates up from here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Billing (TNM)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Time &amp; Material model: team, calendar (holidays/leaves) and expenses -&gt; monthly &amp; yearly billing, profit and margin. Includes a revenue/expense/profit chart and an expense pie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Time &amp; Material: team + calendar + expenses -&gt; monthly &amp; yearly billing, profit and margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Outcome-based conversion: two per-person capacity cases (7 vs 8 SP) with a 20% reserve. Derives velocity, price per story point, margin and the client win-win. Three comparison charts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Outcome conversion: two capacity cases, price per story point, and the client win-win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>One-screen verdict: TNM vs Outcome, who benefits, by how much.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>How to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Edit only the YELLOW cells (team counts, rates, holidays, leaves, expenses, capacity, reserve %, efficiency %, discount %, min invoice).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>All white / shaded cells are formulas and update automatically. Charts redraw on any change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Key assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>One-screen verdict: TNM vs Outcome and who benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Weekends</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>104 days/year. Working days = 365 minus 104 minus holidays minus leaves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Hours/day</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>8 (configurable). Billable hours/year = working days x hours/day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>USD in this model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Formula reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Billable days/year</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>365  -  104 weekends  -  holidays  -  leaves</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+          <t>Key formulas</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Billable days/yr</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>365 - 104 weekends - holidays - leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Monthly billing</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Sum of (count x rate x billable hours per month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Profit margin %</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>(revenue  -  expenses)  /  revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Effective velocity</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>per-person SP  x  headcount  x  (1 - reserve %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Deliverable SP/month</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>effective velocity  x  sprints per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>sum of (count x rate) x billable hours per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Break-even price/SP</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>TNM monthly billing  /  deliverable SP per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>TNM monthly billing / deliverable SP per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Recommended price/SP</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>break-even  x  (1 - client discount %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>break-even x (1 - client discount %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Outcome cost/month</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>TNM monthly cost  /  (1 + efficiency gain %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Outcome margin %</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>(monthly bill  -  outcome cost)  /  monthly bill</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>WIN-WIN test</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>client pays less than TNM  AND  Opus absolute profit is not lower</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Why a client converts (the core insight)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Pay for results</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Under TNM the client pays for TIME and its waste (rework, ramp-up, the 15% meeting/grooming reserve, attrition, rate hikes). Under Outcome the client pays only for ACCEPTED story points at a fixed rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Risk transfer</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Schedule, attrition, ramp-up and estimation risk move from the client to Opus; the client gets price certainty and a throughput SLA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Shared surplus</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Outcome lets Opus KEEP efficiency gains (accelerators / reuse / cheaper mix) that TNM would return as fewer billed hours. Opus prices below the client's TNM cost-per-point and still earns more - both win.</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TNM monthly cost / (1 + efficiency gain %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Win-win test</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>client pays less than TNM AND Opus profit is not lower</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Legend:</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>yellow = input    |    white/blue = formula (do not edit)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="5">
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1803,174 +1838,251 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="002F6FB0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Account Rate Card  -  Apex Bank</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Standard billing rate by role and experience. YELLOW = editable.</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Experience (yrs)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Billing Rate/hr ($)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Key (auto)</t>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Billing Rate/hr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Sr Dev</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>5 to 8</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D5" s="10">
+      <c r="F5" s="15">
         <f>A5&amp;"|"&amp;B5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Sr Dev</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>8 to 10</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="13">
+      <c r="F6" s="15">
         <f>A6&amp;"|"&amp;B6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Tech Lead (Dev)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>9 to 12</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="10">
+      <c r="F7" s="15">
         <f>A7&amp;"|"&amp;B7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Sr QA</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>5 to 8</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D8" s="13">
+      <c r="F8" s="15">
         <f>A8&amp;"|"&amp;B8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Lead QA</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>9 to 12</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="D9" s="10">
+      <c r="F9" s="15">
         <f>A9&amp;"|"&amp;B9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>12 to 14</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="D10" s="13">
+      <c r="F10" s="15">
         <f>A10&amp;"|"&amp;B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>3 to 5</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" s="15">
+        <f>A11&amp;"|"&amp;B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>3 to 5</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="15">
+        <f>A12&amp;"|"&amp;B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>12 to 14</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" s="15">
+        <f>A13&amp;"|"&amp;B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>5 to 8</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="15">
+        <f>A14&amp;"|"&amp;B14</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1983,622 +2095,673 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="2" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Billing Simulator  -  Time &amp; Material (TNM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+          <t>Billing Simulator - Time &amp; Material (TNM)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>YELLOW = inputs. Revenue, profit and margin are live formulas.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Company calendar &amp; hours</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Hours per day</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>Monthly ($)</t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="I5" s="21">
+        <f>B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Weekend days / year</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B6" s="22" t="n">
         <v>104</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="I5" s="19">
-        <f>B33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="I6" s="21">
+        <f>B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Public holidays / year</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B7" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="I6" s="19">
-        <f>B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="I7" s="21">
+        <f>B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Leaves / year</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B8" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>Profit</t>
-        </is>
-      </c>
-      <c r="I7" s="19">
-        <f>B37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Billable days / year</t>
         </is>
       </c>
-      <c r="B8" s="17">
-        <f>365-B5-B6-B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="B9" s="22">
+        <f>365-B6-B7-B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Billable hours / year (per resource)</t>
         </is>
       </c>
-      <c r="B9" s="17">
-        <f>B8*B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="B10" s="22">
+        <f>B9*B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Billable hours / month (per resource)</t>
         </is>
       </c>
-      <c r="B10" s="20">
-        <f>B9/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Project team</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B11" s="23">
+        <f>B10/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Project team   (pick role &amp; experience - rate auto-fills from the Rate Card)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Rate/hr</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Yearly Revenue</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Sr Dev</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>5 to 8</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="21">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A14&amp;"|"&amp;B14,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E14" s="22">
-        <f>C14*D14*$B$10</f>
-        <v/>
-      </c>
-      <c r="F14" s="22">
-        <f>C14*D14*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="D15" s="26">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A15&amp;"|"&amp;B15,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>C15*D15*$B$11</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>C15*D15*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Sr Dev</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>8 to 10</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="23">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A15&amp;"|"&amp;B15,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>C15*D15*$B$10</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
-        <f>C15*D15*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="D16" s="28">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A16&amp;"|"&amp;B16,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="29">
+        <f>C16*D16*$B$11</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>C16*D16*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Tech Lead (Dev)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>9 to 12</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="21">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A16&amp;"|"&amp;B16,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E16" s="22">
-        <f>C16*D16*$B$10</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f>C16*D16*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="D17" s="26">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A17&amp;"|"&amp;B17,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>C17*D17*$B$11</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>C17*D17*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Sr QA</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>5 to 8</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="23">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A17&amp;"|"&amp;B17,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E17" s="24">
-        <f>C17*D17*$B$10</f>
-        <v/>
-      </c>
-      <c r="F17" s="24">
-        <f>C17*D17*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="D18" s="28">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A18&amp;"|"&amp;B18,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>C18*D18*$B$11</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>C18*D18*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Lead QA</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>9 to 12</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C19" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="21">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A18&amp;"|"&amp;B18,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E18" s="22">
-        <f>C18*D18*$B$10</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>C18*D18*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="D19" s="26">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A19&amp;"|"&amp;B19,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>C19*D19*$B$11</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>C19*D19*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>12 to 14</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="23">
-        <f>INDEX('Rate Card'!$C$5:$C$10,MATCH(A19&amp;"|"&amp;B19,'Rate Card'!$D$5:$D$10,0))</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>C19*D19*$B$10</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>C19*D19*$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="D20" s="28">
+        <f>IFERROR(INDEX('Rate Card'!$C$5:$C$14,MATCH(A20&amp;"|"&amp;B20,'Rate Card'!$F$5:$F$14,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>C20*D20*$B$11</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>C20*D20*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>Total team</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="27">
-        <f>SUM(C14:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="28" t="inlineStr"/>
-      <c r="E20" s="29">
-        <f>SUM(E14:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="29">
-        <f>SUM(F14:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="32">
+        <f>SUM(C15:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="33">
+        <f>SUM(E15:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="33">
+        <f>SUM(F15:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Project expenses (cost)</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Yearly Amount</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Salaries</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B25" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="D24" s="22">
-        <f>IF(C24="monthly",B24*12,B24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="D25" s="27">
+        <f>IF(C25="monthly",B25*12,B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Infrastructure / seats</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B26" s="34" t="n">
         <v>2500</v>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="D25" s="24">
-        <f>IF(C25="monthly",B25*12,B25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="D26" s="29">
+        <f>IF(C26="monthly",B26*12,B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Software licenses</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B27" s="34" t="n">
         <v>1200</v>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="D26" s="22">
-        <f>IF(C26="monthly",B26*12,B26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="D27" s="27">
+        <f>IF(C27="monthly",B27*12,B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B28" s="34" t="n">
         <v>700</v>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="D27" s="24">
-        <f>IF(C27="monthly",B27*12,B27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="D28" s="29">
+        <f>IF(C28="monthly",B28*12,B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B29" s="34" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>yearly</t>
         </is>
       </c>
-      <c r="D28" s="22">
-        <f>IF(C28="monthly",B28*12,B28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="D29" s="27">
+        <f>IF(C29="monthly",B29*12,B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Total yearly expenses</t>
         </is>
       </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="29">
-        <f>SUM(D24:D28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="33">
+        <f>SUM(D25:D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Total monthly expenses</t>
         </is>
       </c>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="29">
-        <f>D29/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="33">
+        <f>D30/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>Monthly billing (revenue)</t>
         </is>
       </c>
-      <c r="B33" s="33">
-        <f>E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="B34" s="36">
+        <f>E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Yearly billing (revenue)</t>
         </is>
       </c>
-      <c r="B34" s="35">
-        <f>F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="B35" s="37">
+        <f>F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>Monthly expenses (cost)</t>
         </is>
       </c>
-      <c r="B35" s="33">
+      <c r="B36" s="36">
+        <f>D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Yearly expenses (cost)</t>
+        </is>
+      </c>
+      <c r="B37" s="37">
         <f>D30</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="34" t="inlineStr">
-        <is>
-          <t>Yearly expenses (cost)</t>
-        </is>
-      </c>
-      <c r="B36" s="35">
-        <f>D29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>Monthly profit</t>
         </is>
       </c>
-      <c r="B37" s="33">
-        <f>B33-B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="B38" s="36">
+        <f>B34-B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Yearly profit</t>
         </is>
       </c>
-      <c r="B38" s="35">
-        <f>B34-B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="B39" s="37">
+        <f>B35-B37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Profit margin %</t>
         </is>
       </c>
-      <c r="B39" s="37">
-        <f>B38/B34</f>
+      <c r="B40" s="39">
+        <f>IFERROR(B39/B35,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
+  <conditionalFormatting sqref="D15:D20">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"8,9"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C25:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"monthly,yearly"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A15:A20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Architect,Business Analyst,Developer,Lead QA,PO,QA Engineer,Sr Dev,Sr QA,Tech Lead (Dev)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15:B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0 to 3,3 to 5,5 to 8,8 to 10,9 to 12,12 to 14"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2611,584 +2774,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="2" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="11" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Outcome-Based Cost Simulation</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Two capacity cases. YELLOW = inputs. Team &amp; cost inherited from Billing (TNM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Two capacity cases. YELLOW = inputs. Team &amp; cost are inherited from Billing (TNM).</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Headcount (from Billing)</t>
         </is>
       </c>
-      <c r="B4" s="17">
-        <f>'Billing (TNM)'!C20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Per-person SP / sprint  -  Case 1</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="32">
+        <f>'Billing (TNM)'!C21</f>
+        <v/>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Client pays</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>TNM</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Per-person SP / sprint - Case 1</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Per-person SP / sprint  -  Case 2</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="n">
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
+      <c r="O6" s="21">
+        <f>$B$13</f>
+        <v/>
+      </c>
+      <c r="P6" s="21">
+        <f>B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Per-person SP / sprint - Case 2</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>Case 2</t>
+        </is>
+      </c>
+      <c r="O7" s="21">
+        <f>$B$13</f>
+        <v/>
+      </c>
+      <c r="P7" s="21">
+        <f>C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Capacity reserve %</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B8" s="41" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Sprints per month</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B9" s="19" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>Opus margin</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>TNM</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Minimum invoice SP</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B10" s="19" t="n">
         <v>120</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
+      <c r="O10" s="42">
+        <f>B28</f>
+        <v/>
+      </c>
+      <c r="P10" s="42">
+        <f>B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Outcome efficiency gain %</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n">
+      <c r="B11" s="41" t="n">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>Case 2</t>
+        </is>
+      </c>
+      <c r="O11" s="42">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="P11" s="42">
+        <f>C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Client discount %</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n">
+      <c r="B12" s="41" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>TNM monthly billing (R)</t>
-        </is>
-      </c>
-      <c r="B12" s="39">
-        <f>'Billing (TNM)'!$B$33</f>
-        <v/>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Monthly cost (C)</t>
-        </is>
-      </c>
-      <c r="B13" s="39">
-        <f>'Billing (TNM)'!$B$35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Case 1 vs Case 2  -  step-by-step</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>TNM monthly billing  (R)</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>'Billing (TNM)'!$B$34</f>
+        <v/>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>Price / SP</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>Break-even</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Monthly cost  (C)</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>'Billing (TNM)'!$B$36</f>
+        <v/>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
+      <c r="O14" s="43">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="P14" s="43">
+        <f>B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>Case 2</t>
+        </is>
+      </c>
+      <c r="O15" s="43">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="P15" s="43">
+        <f>C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Case 1 vs Case 2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Case 1</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Case 2</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>Client pays</t>
-        </is>
-      </c>
-      <c r="O16" s="16" t="inlineStr">
-        <is>
-          <t>TNM</t>
-        </is>
-      </c>
-      <c r="P16" s="16" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Per-person SP / sprint</t>
         </is>
       </c>
-      <c r="B17" s="40">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="C17" s="40">
+      <c r="B18" s="44">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="N17" s="18" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
-      <c r="O17" s="19">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="P17" s="19">
-        <f>B24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="C18" s="44">
+        <f>$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gross team velocity / sprint</t>
         </is>
       </c>
-      <c r="B18" s="41">
-        <f>B17*$B$4</f>
-        <v/>
-      </c>
-      <c r="C18" s="41">
-        <f>C17*$B$4</f>
-        <v/>
-      </c>
-      <c r="N18" s="18" t="inlineStr">
-        <is>
-          <t>Case 2</t>
-        </is>
-      </c>
-      <c r="O18" s="19">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="P18" s="19">
-        <f>C24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="B19" s="45">
+        <f>B18*$B$5</f>
+        <v/>
+      </c>
+      <c r="C19" s="45">
+        <f>C18*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Effective velocity (after reserve)</t>
         </is>
       </c>
-      <c r="B19" s="42">
-        <f>B18*(1-$B$7)</f>
-        <v/>
-      </c>
-      <c r="C19" s="42">
-        <f>C18*(1-$B$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="B20" s="46">
+        <f>B19*(1-$B$8)</f>
+        <v/>
+      </c>
+      <c r="C20" s="46">
+        <f>C19*(1-$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Deliverable SP / month</t>
         </is>
       </c>
-      <c r="B20" s="43">
-        <f>B19*$B$8</f>
-        <v/>
-      </c>
-      <c r="C20" s="43">
-        <f>C19*$B$8</f>
-        <v/>
-      </c>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>Opus margin</t>
-        </is>
-      </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>TNM</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B21" s="47">
+        <f>B20*$B$9</f>
+        <v/>
+      </c>
+      <c r="C21" s="47">
+        <f>C20*$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Meets min invoice?</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>IF(B20&gt;=$B$9,"Yes","No (short "&amp;TEXT($B$9-B20,"0")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="C21" s="8">
-        <f>IF(C20&gt;=$B$9,"Yes","No (short "&amp;TEXT($B$9-C20,"0")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
-      <c r="O21" s="44">
-        <f>B27</f>
-        <v/>
-      </c>
-      <c r="P21" s="44">
-        <f>B28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="B22" s="13">
+        <f>IF(B21&gt;=$B$10,"Yes","No (short)")</f>
+        <v/>
+      </c>
+      <c r="C22" s="13">
+        <f>IF(C21&gt;=$B$10,"Yes","No (short)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Break-even price / SP</t>
         </is>
       </c>
-      <c r="B22" s="23">
-        <f>$B$12/B20</f>
-        <v/>
-      </c>
-      <c r="C22" s="23">
-        <f>$B$12/C20</f>
-        <v/>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t>Case 2</t>
-        </is>
-      </c>
-      <c r="O22" s="44">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="P22" s="44">
-        <f>C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="B23" s="28">
+        <f>IFERROR($B$13/B21,0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>IFERROR($B$13/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Recommended price / SP</t>
         </is>
       </c>
-      <c r="B23" s="45">
-        <f>B22*(1-$B$11)</f>
-        <v/>
-      </c>
-      <c r="C23" s="45">
-        <f>C22*(1-$B$11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="B24" s="48">
+        <f>B23*(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="C24" s="48">
+        <f>C23*(1-$B$12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>Monthly outcome bill</t>
         </is>
       </c>
-      <c r="B24" s="46">
-        <f>B23*B20</f>
-        <v/>
-      </c>
-      <c r="C24" s="46">
-        <f>C23*C20</f>
-        <v/>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>Price/SP</t>
-        </is>
-      </c>
-      <c r="O24" s="16" t="inlineStr">
-        <is>
-          <t>Break-even</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="B25" s="49">
+        <f>B24*B21</f>
+        <v/>
+      </c>
+      <c r="C25" s="49">
+        <f>C24*C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Yearly outcome bill</t>
         </is>
       </c>
-      <c r="B25" s="47">
-        <f>B24*12</f>
-        <v/>
-      </c>
-      <c r="C25" s="47">
-        <f>C24*12</f>
-        <v/>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
-      <c r="O25" s="48">
-        <f>B22</f>
-        <v/>
-      </c>
-      <c r="P25" s="48">
-        <f>B23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B26" s="27">
+        <f>B25*12</f>
+        <v/>
+      </c>
+      <c r="C26" s="27">
+        <f>C25*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Outcome cost / month</t>
         </is>
       </c>
-      <c r="B26" s="49">
-        <f>$B$13/(1+$B$10)</f>
-        <v/>
-      </c>
-      <c r="C26" s="49">
-        <f>$B$13/(1+$B$10)</f>
-        <v/>
-      </c>
-      <c r="N26" s="18" t="inlineStr">
-        <is>
-          <t>Case 2</t>
-        </is>
-      </c>
-      <c r="O26" s="48">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="P26" s="48">
-        <f>C23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Opus margin  -  TNM</t>
-        </is>
-      </c>
-      <c r="B27" s="50">
-        <f>($B$12-$B$13)/$B$12</f>
-        <v/>
-      </c>
-      <c r="C27" s="50">
-        <f>($B$12-$B$13)/$B$12</f>
+      <c r="B27" s="29">
+        <f>IFERROR($B$14/(1+$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>IFERROR($B$14/(1+$B$11),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>Opus margin  -  Outcome</t>
-        </is>
-      </c>
-      <c r="B28" s="51">
-        <f>(B24-B26)/B24</f>
-        <v/>
-      </c>
-      <c r="C28" s="51">
-        <f>(C24-C26)/C24</f>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Opus margin - TNM</t>
+        </is>
+      </c>
+      <c r="B28" s="50">
+        <f>IFERROR(($B$13-$B$14)/$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="50">
+        <f>IFERROR(($B$13-$B$14)/$B$13,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Margin uplift (pts)</t>
-        </is>
-      </c>
-      <c r="B29" s="50">
-        <f>B28-B27</f>
-        <v/>
-      </c>
-      <c r="C29" s="50">
-        <f>C28-C27</f>
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>Opus margin - Outcome</t>
+        </is>
+      </c>
+      <c r="B29" s="51">
+        <f>IFERROR((B25-B27)/B25,0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="51">
+        <f>IFERROR((C25-C27)/C25,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Opus profit  -  TNM / month</t>
-        </is>
-      </c>
-      <c r="B30" s="49">
-        <f>$B$12-$B$13</f>
-        <v/>
-      </c>
-      <c r="C30" s="49">
-        <f>$B$12-$B$13</f>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Margin uplift</t>
+        </is>
+      </c>
+      <c r="B30" s="50">
+        <f>B29-B28</f>
+        <v/>
+      </c>
+      <c r="C30" s="50">
+        <f>C29-C28</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Opus profit  -  Outcome / month</t>
-        </is>
-      </c>
-      <c r="B31" s="47">
-        <f>B24-B26</f>
-        <v/>
-      </c>
-      <c r="C31" s="47">
-        <f>C24-C26</f>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Opus profit - TNM / month</t>
+        </is>
+      </c>
+      <c r="B31" s="29">
+        <f>$B$13-$B$14</f>
+        <v/>
+      </c>
+      <c r="C31" s="29">
+        <f>$B$13-$B$14</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Opus profit - Outcome / month</t>
+        </is>
+      </c>
+      <c r="B32" s="27">
+        <f>B25-B27</f>
+        <v/>
+      </c>
+      <c r="C32" s="27">
+        <f>C25-C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>Opus extra profit / year</t>
         </is>
       </c>
-      <c r="B32" s="46">
-        <f>(B31-B30)*12</f>
-        <v/>
-      </c>
-      <c r="C32" s="46">
-        <f>(C31-C30)*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B33" s="49">
+        <f>(B32-B31)*12</f>
+        <v/>
+      </c>
+      <c r="C33" s="49">
+        <f>(C32-C31)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Client saving / month</t>
         </is>
       </c>
-      <c r="B33" s="47">
-        <f>$B$12-B24</f>
-        <v/>
-      </c>
-      <c r="C33" s="47">
-        <f>$B$12-C24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="B34" s="27">
+        <f>$B$13-B25</f>
+        <v/>
+      </c>
+      <c r="C34" s="27">
+        <f>$B$13-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>Client saving / year</t>
         </is>
       </c>
-      <c r="B34" s="46">
-        <f>B33*12</f>
-        <v/>
-      </c>
-      <c r="C34" s="46">
-        <f>C33*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="B35" s="49">
+        <f>B34*12</f>
+        <v/>
+      </c>
+      <c r="C35" s="49">
+        <f>C34*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>WIN-WIN?</t>
         </is>
       </c>
-      <c r="B35" s="52">
-        <f>IF(AND(B24&lt;$B$12,(B24-B26)&gt;=($B$12-$B$13)),"YES - WIN-WIN","Not yet")</f>
-        <v/>
-      </c>
-      <c r="C35" s="52">
-        <f>IF(AND(C24&lt;$B$12,(C24-C26)&gt;=($B$12-$B$13)),"YES - WIN-WIN","Not yet")</f>
+      <c r="B36" s="52">
+        <f>IF(AND(B25&lt;$B$13,(B25-B27)&gt;=($B$13-$B$14)),"YES - WIN-WIN","Not yet")</f>
+        <v/>
+      </c>
+      <c r="C36" s="52">
+        <f>IF(AND(C25&lt;$B$13,(C25-C27)&gt;=($B$13-$B$14)),"YES - WIN-WIN","Not yet")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>ISNUMBER(SEARCH("WIN",B36))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>NOT(ISNUMBER(SEARCH("WIN",B36)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>ISNUMBER(SEARCH("WIN",C36))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>NOT(ISNUMBER(SEARCH("WIN",C36)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3201,164 +3388,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dashboard  -  TNM vs Outcome (Case 2, feasible)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+          <t>Dashboard - TNM vs Outcome (Case 2, feasible)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Headline verdict for the 8 SP/person case.</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Key numbers</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Headline numbers</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Who benefits (annual $)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>TNM monthly billing</t>
         </is>
       </c>
-      <c r="B5" s="53">
-        <f>'Outcome'!$B$12</f>
-        <v/>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="B5" s="54">
+        <f>Outcome!B13</f>
+        <v/>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Client saving</t>
         </is>
       </c>
-      <c r="E5" s="19">
-        <f>'Outcome'!C34</f>
+      <c r="E5" s="21">
+        <f>Outcome!C35</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>TNM yearly billing</t>
         </is>
       </c>
-      <c r="B6" s="54">
-        <f>'Outcome'!$B$12*12</f>
-        <v/>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="B6" s="55">
+        <f>Outcome!B13*12</f>
+        <v/>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Opus extra profit</t>
         </is>
       </c>
-      <c r="E6" s="19">
-        <f>'Outcome'!C32</f>
+      <c r="E6" s="21">
+        <f>Outcome!C33</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>TNM margin</t>
         </is>
       </c>
-      <c r="B7" s="55">
-        <f>'Outcome'!C27</f>
+      <c r="B7" s="56">
+        <f>Outcome!C28</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Outcome monthly bill</t>
         </is>
       </c>
-      <c r="B8" s="54">
-        <f>'Outcome'!C24</f>
+      <c r="B8" s="55">
+        <f>Outcome!C25</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Outcome margin</t>
         </is>
       </c>
-      <c r="B9" s="56">
-        <f>'Outcome'!C28</f>
+      <c r="B9" s="39">
+        <f>Outcome!C29</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Opus extra profit / year</t>
         </is>
       </c>
       <c r="B10" s="57">
-        <f>'Outcome'!C32</f>
+        <f>Outcome!C33</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Client saving / year</t>
         </is>
       </c>
       <c r="B11" s="57">
-        <f>'Outcome'!C34</f>
+        <f>Outcome!C35</f>
         <v/>
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13">
       <c r="A13" s="58">
-        <f>'Outcome'!C35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
+        <f>Outcome!C36</f>
+        <v/>
+      </c>
+      <c r="B13" s="59" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="n"/>
+      <c r="B14" s="60" t="n"/>
+    </row>
     <row r="15"/>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
-        <is>
-          <t>Both parties end up better off: the client pays less than TNM while Opus earns more - because Outcome lets Opus keep the efficiency gain that TNM would have handed back as fewer billed hours.</t>
+    <row r="16">
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>Both parties end up better off: the client pays less than TNM while Opus earns more - the efficiency Opus keeps under Outcome funds a price the client still finds cheaper.</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A16:B21"/>
     <mergeCell ref="A13:B14"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A16:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>ISNUMBER(SEARCH("WIN",A13))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>NOT(ISNUMBER(SEARCH("WIN",A13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
